--- a/事務所檢查系統/input/選案參數_115安永.xlsx
+++ b/事務所檢查系統/input/選案參數_115安永.xlsx
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1147,6 +1147,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>安永同時出具114年度溫室氣體確信報告，擬一併調閱確信工作底稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>指定納入</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>永續主軸：台塑集團碳費衝擊極高（114年範疇一排放約2,435萬噸），台塑化為安永簽證之集團公司；台塑(1301)、南亞(1303)由安侯建業、台化(1326)由資誠簽證，非安永客戶</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1310,6 @@
       <c r="B2" t="n">
         <v>114</v>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1299,7 +1320,6 @@
       <c r="B3" t="n">
         <v>114</v>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1310,7 +1330,6 @@
       <c r="B4" t="n">
         <v>113</v>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1321,7 +1340,6 @@
       <c r="B5" t="n">
         <v>113</v>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1368,7 +1386,6 @@
           <t>馬施云大華</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1379,7 +1396,6 @@
       <c r="B10" t="n">
         <v>114</v>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1387,7 +1403,6 @@
           <t>建智</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
